--- a/logs/duplicate_transactions_shell.xlsx
+++ b/logs/duplicate_transactions_shell.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,65 +460,75 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>start_mins</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>enddate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>endhour</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>end_mins</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>port</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>supplier_n</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>supplier1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>supplier2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>supplier3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>supplier4</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>supplier5</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>supplier6</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>supplier7</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>supplier8</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>supplier9</t>
         </is>
@@ -542,37 +552,43 @@
       <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>45232</v>
       </c>
-      <c r="G2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>41</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Heng Xing 9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Hongheng169</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -592,22 +608,26 @@
       <c r="E3" t="n">
         <v>7</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>45232</v>
       </c>
-      <c r="G3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -615,6 +635,8 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,35 +654,41 @@
         <v>45239</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>45239</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>15</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Run Ze 11</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -678,24 +706,28 @@
         <v>45239</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>45239</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>15</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -703,6 +735,8 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -720,39 +754,45 @@
         <v>45439</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>41</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>45440</v>
       </c>
-      <c r="G6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>47</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Fu Jie 168</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Hong Zhou You 27</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -770,24 +810,28 @@
         <v>45439</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>45440</v>
       </c>
-      <c r="G7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>47</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -795,6 +839,8 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -812,35 +858,41 @@
         <v>45303</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
-      </c>
-      <c r="F8" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" t="n">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>45304</v>
       </c>
-      <c r="G8" t="n">
-        <v>17</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" t="n">
+        <v>42</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -858,24 +910,28 @@
         <v>45303</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
-      </c>
-      <c r="F9" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>42</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>45304</v>
       </c>
-      <c r="G9" t="n">
-        <v>17</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>42</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -883,6 +939,8 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -902,33 +960,39 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>17</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Ning Feng You 1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -948,22 +1012,26 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>17</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>17</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -971,6 +1039,8 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -990,33 +1060,39 @@
       <c r="E12" t="n">
         <v>18</v>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>45354</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>45353</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Shenfengzhou</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1036,22 +1112,26 @@
       <c r="E13" t="n">
         <v>18</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>45354</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>45353</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23</v>
+      </c>
+      <c r="I13" t="n">
+        <v>32</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1059,6 +1139,8 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1078,33 +1160,39 @@
       <c r="E14" t="n">
         <v>23</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>45269</v>
       </c>
-      <c r="G14" t="n">
-        <v>15</v>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>33</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Kang--Fa--125</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1124,22 +1212,26 @@
       <c r="E15" t="n">
         <v>23</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" t="n">
+        <v>19</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>45269</v>
       </c>
-      <c r="G15" t="n">
-        <v>15</v>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>33</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -1147,6 +1239,8 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1164,39 +1258,45 @@
         <v>45324</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>45</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>45325</v>
       </c>
-      <c r="G16" t="n">
-        <v>15</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" t="n">
+        <v>14</v>
+      </c>
+      <c r="I16" t="n">
+        <v>45</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Kang Fa 86</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Fu Jie 168</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1214,24 +1314,28 @@
         <v>45324</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>45325</v>
       </c>
-      <c r="G17" t="n">
-        <v>15</v>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" t="n">
+        <v>45</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -1239,6 +1343,8 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1256,35 +1362,41 @@
         <v>44934</v>
       </c>
       <c r="E18" t="n">
-        <v>22</v>
-      </c>
-      <c r="F18" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" t="n">
+        <v>40</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>44935</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>11</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Da Dong Kai 11</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1302,24 +1414,28 @@
         <v>44934</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
-      </c>
-      <c r="F19" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>44935</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>11</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -1327,6 +1443,8 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1344,24 +1462,28 @@
         <v>44934</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
-      </c>
-      <c r="F20" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F20" t="n">
+        <v>40</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>44935</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>11</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -1369,6 +1491,8 @@
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1388,41 +1512,47 @@
       <c r="E21" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <v>45102</v>
       </c>
-      <c r="G21" t="n">
-        <v>11</v>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
+        <v>41</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Hongheng169</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Hongheng169</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1442,22 +1572,26 @@
       <c r="E22" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>45102</v>
       </c>
-      <c r="G22" t="n">
-        <v>11</v>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n">
+        <v>41</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -1465,6 +1599,8 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1484,33 +1620,39 @@
       <c r="E23" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>44936</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>10</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>21</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Yong Cheng 166</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1530,22 +1672,26 @@
       <c r="E24" t="n">
         <v>4</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>44936</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>10</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>21</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -1553,6 +1699,8 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1572,33 +1720,39 @@
       <c r="E25" t="n">
         <v>19</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" t="n">
+        <v>13</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>45422</v>
       </c>
-      <c r="G25" t="n">
-        <v>11</v>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" t="n">
+        <v>47</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Run Ze 11</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1618,22 +1772,26 @@
       <c r="E26" t="n">
         <v>19</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" t="n">
+        <v>13</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>45422</v>
       </c>
-      <c r="G26" t="n">
-        <v>11</v>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" t="n">
+        <v>47</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -1641,6 +1799,8 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1658,39 +1818,45 @@
         <v>44990</v>
       </c>
       <c r="E27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" t="n">
+        <v>55</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>44991</v>
+      </c>
+      <c r="H27" t="n">
         <v>16</v>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>44991</v>
-      </c>
-      <c r="G27" t="n">
-        <v>16</v>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>虾峙门</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Chaoyang301</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Kang Fa 86</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1708,24 +1874,28 @@
         <v>44990</v>
       </c>
       <c r="E28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" t="n">
+        <v>55</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>44991</v>
+      </c>
+      <c r="H28" t="n">
         <v>16</v>
       </c>
-      <c r="F28" s="2" t="n">
-        <v>44991</v>
-      </c>
-      <c r="G28" t="n">
-        <v>16</v>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>虾峙门</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -1733,6 +1903,8 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1752,33 +1924,39 @@
       <c r="E29" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>45389</v>
       </c>
-      <c r="G29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>31</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Run Ze 11</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1798,22 +1976,26 @@
       <c r="E30" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" t="n">
+        <v>16</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>45389</v>
       </c>
-      <c r="G30" t="n">
-        <v>4</v>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>31</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -1821,6 +2003,8 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1838,35 +2022,41 @@
         <v>45264</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
-      </c>
-      <c r="F31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>41</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>45264</v>
       </c>
-      <c r="G31" t="n">
-        <v>18</v>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" t="n">
+        <v>17</v>
+      </c>
+      <c r="I31" t="n">
+        <v>40</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Qi Chen 6</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1884,24 +2074,28 @@
         <v>45264</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
-      </c>
-      <c r="F32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>41</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>45264</v>
       </c>
-      <c r="G32" t="n">
-        <v>18</v>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" t="n">
+        <v>17</v>
+      </c>
+      <c r="I32" t="n">
+        <v>40</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -1909,6 +2103,8 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1928,41 +2124,47 @@
       <c r="E33" t="n">
         <v>19</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" t="n">
+        <v>17</v>
+      </c>
+      <c r="G33" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>12</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>3</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Guoyang178</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Guoyang178</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Yicheng27</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1982,22 +2184,26 @@
       <c r="E34" t="n">
         <v>19</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" t="n">
+        <v>17</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>12</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -2005,6 +2211,8 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2024,37 +2232,43 @@
       <c r="E35" t="n">
         <v>19</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" t="n">
+        <v>27</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <v>45405</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>12</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Kang--Fa--125</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Shun Ping 17</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2074,22 +2288,26 @@
       <c r="E36" t="n">
         <v>19</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" t="n">
+        <v>27</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>45405</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>12</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -2097,6 +2315,8 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2116,37 +2336,43 @@
       <c r="E37" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="n">
         <v>45198</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>4</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>虾峙门</t>
-        </is>
       </c>
       <c r="I37" t="n">
         <v>2</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>虾峙门</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>Qi Chen 6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Qi Chen 6</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2166,22 +2392,26 @@
       <c r="E38" t="n">
         <v>12</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
         <v>45198</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>4</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>虾峙门</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -2189,6 +2419,8 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2208,33 +2440,39 @@
       <c r="E39" t="n">
         <v>16</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" t="n">
+        <v>15</v>
+      </c>
+      <c r="G39" s="2" t="n">
         <v>45132</v>
       </c>
-      <c r="G39" t="n">
-        <v>9</v>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" t="n">
+        <v>8</v>
+      </c>
+      <c r="I39" t="n">
+        <v>41</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Zhou Shun 10</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2254,22 +2492,26 @@
       <c r="E40" t="n">
         <v>16</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" t="n">
+        <v>15</v>
+      </c>
+      <c r="G40" s="2" t="n">
         <v>45132</v>
       </c>
-      <c r="G40" t="n">
-        <v>9</v>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" t="n">
+        <v>8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>41</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -2277,6 +2519,8 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2294,35 +2538,41 @@
         <v>45427</v>
       </c>
       <c r="E41" t="n">
-        <v>13</v>
-      </c>
-      <c r="F41" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F41" t="n">
+        <v>30</v>
+      </c>
+      <c r="G41" s="2" t="n">
         <v>45428</v>
       </c>
-      <c r="G41" t="n">
-        <v>8</v>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="n">
+        <v>7</v>
+      </c>
+      <c r="I41" t="n">
+        <v>47</v>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2340,24 +2590,28 @@
         <v>45427</v>
       </c>
       <c r="E42" t="n">
-        <v>13</v>
-      </c>
-      <c r="F42" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" t="n">
+        <v>30</v>
+      </c>
+      <c r="G42" s="2" t="n">
         <v>45428</v>
       </c>
-      <c r="G42" t="n">
-        <v>8</v>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I42" t="n">
+        <v>47</v>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -2365,6 +2619,8 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2384,33 +2640,39 @@
       <c r="E43" t="n">
         <v>23</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F43" t="n">
+        <v>21</v>
+      </c>
+      <c r="G43" s="2" t="n">
         <v>45245</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>8</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>秀山东</t>
-        </is>
       </c>
       <c r="I43" t="n">
         <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>秀山东</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>Run Ze 11</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2430,22 +2692,26 @@
       <c r="E44" t="n">
         <v>23</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" t="n">
+        <v>21</v>
+      </c>
+      <c r="G44" s="2" t="n">
         <v>45245</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>8</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -2453,6 +2719,8 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2472,33 +2740,39 @@
       <c r="E45" t="n">
         <v>7</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F45" t="n">
+        <v>16</v>
+      </c>
+      <c r="G45" s="2" t="n">
         <v>45060</v>
       </c>
-      <c r="G45" t="n">
-        <v>22</v>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" t="n">
+        <v>21</v>
+      </c>
+      <c r="I45" t="n">
+        <v>42</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>1</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Guoyang178</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2518,22 +2792,26 @@
       <c r="E46" t="n">
         <v>7</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" t="n">
+        <v>16</v>
+      </c>
+      <c r="G46" s="2" t="n">
         <v>45060</v>
       </c>
-      <c r="G46" t="n">
-        <v>22</v>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" t="n">
+        <v>21</v>
+      </c>
+      <c r="I46" t="n">
+        <v>42</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -2541,6 +2819,8 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2558,35 +2838,41 @@
         <v>45254</v>
       </c>
       <c r="E47" t="n">
-        <v>8</v>
-      </c>
-      <c r="F47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F47" t="n">
+        <v>57</v>
+      </c>
+      <c r="G47" s="2" t="n">
         <v>45255</v>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>1</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Kang Fa 86</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2604,24 +2890,28 @@
         <v>45254</v>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
-      </c>
-      <c r="F48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F48" t="n">
+        <v>57</v>
+      </c>
+      <c r="G48" s="2" t="n">
         <v>45255</v>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -2629,6 +2919,8 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2648,37 +2940,43 @@
       <c r="E49" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" t="n">
+        <v>22</v>
+      </c>
+      <c r="G49" s="2" t="n">
         <v>45245</v>
       </c>
-      <c r="G49" t="n">
-        <v>11</v>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" t="n">
+        <v>40</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>2</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Kang--Fa--125</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Kang--Fa--125</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2698,22 +2996,26 @@
       <c r="E50" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" t="n">
+        <v>22</v>
+      </c>
+      <c r="G50" s="2" t="n">
         <v>45245</v>
       </c>
-      <c r="G50" t="n">
-        <v>11</v>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" t="n">
+        <v>40</v>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -2721,6 +3023,8 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2740,37 +3044,43 @@
       <c r="E51" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2" t="n">
         <v>44999</v>
       </c>
-      <c r="G51" t="n">
-        <v>17</v>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" t="n">
+        <v>16</v>
+      </c>
+      <c r="I51" t="n">
+        <v>40</v>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>2</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Zhe Hai You 5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Zhe Hai You 5</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2790,22 +3100,26 @@
       <c r="E52" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2" t="n">
         <v>44999</v>
       </c>
-      <c r="G52" t="n">
-        <v>17</v>
-      </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" t="n">
+        <v>16</v>
+      </c>
+      <c r="I52" t="n">
+        <v>40</v>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -2813,6 +3127,8 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2832,33 +3148,39 @@
       <c r="E53" t="n">
         <v>15</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="G53" t="n">
-        <v>10</v>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" t="n">
+        <v>9</v>
+      </c>
+      <c r="I53" t="n">
+        <v>59</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>1</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Qi Chen 6</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2878,22 +3200,26 @@
       <c r="E54" t="n">
         <v>15</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="G54" t="n">
-        <v>10</v>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" t="n">
+        <v>9</v>
+      </c>
+      <c r="I54" t="n">
+        <v>59</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -2901,6 +3227,8 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2920,41 +3248,47 @@
       <c r="E55" t="n">
         <v>20</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" t="n">
+        <v>16</v>
+      </c>
+      <c r="G55" s="2" t="n">
         <v>44954</v>
       </c>
-      <c r="G55" t="n">
-        <v>18</v>
-      </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" t="n">
+        <v>17</v>
+      </c>
+      <c r="I55" t="n">
+        <v>56</v>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>3</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Rui Yun 21</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Zhong Xing You 6</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Zhong Xing You 6</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2974,22 +3308,26 @@
       <c r="E56" t="n">
         <v>20</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" t="n">
+        <v>16</v>
+      </c>
+      <c r="G56" s="2" t="n">
         <v>44954</v>
       </c>
-      <c r="G56" t="n">
-        <v>18</v>
-      </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" t="n">
+        <v>17</v>
+      </c>
+      <c r="I56" t="n">
+        <v>56</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -2997,6 +3335,8 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3014,35 +3354,41 @@
         <v>45248</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" t="n">
+        <v>55</v>
+      </c>
+      <c r="G57" s="2" t="n">
         <v>45249</v>
       </c>
-      <c r="G57" t="n">
-        <v>15</v>
-      </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" t="n">
+        <v>14</v>
+      </c>
+      <c r="I57" t="n">
+        <v>42</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>虾峙门</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>1</v>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Yi Da 5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3060,24 +3406,28 @@
         <v>45248</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
-      </c>
-      <c r="F58" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>55</v>
+      </c>
+      <c r="G58" s="2" t="n">
         <v>45249</v>
       </c>
-      <c r="G58" t="n">
-        <v>15</v>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" t="n">
+        <v>14</v>
+      </c>
+      <c r="I58" t="n">
+        <v>42</v>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>虾峙门</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -3085,6 +3435,8 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3102,39 +3454,45 @@
         <v>45345</v>
       </c>
       <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>43</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>45346</v>
+      </c>
+      <c r="H59" t="n">
+        <v>9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>17</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>秀山东</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="2" t="n">
-        <v>45346</v>
-      </c>
-      <c r="G59" t="n">
-        <v>9</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>秀山东</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>Yi Cheng 26</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Sijie15</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3152,24 +3510,28 @@
         <v>45345</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>43</v>
+      </c>
+      <c r="G60" s="2" t="n">
         <v>45346</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>9</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>17</v>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>秀山东</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -3177,6 +3539,8 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3196,37 +3560,43 @@
       <c r="E61" t="n">
         <v>17</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
         <v>44917</v>
       </c>
-      <c r="G61" t="n">
-        <v>11</v>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" t="n">
+        <v>10</v>
+      </c>
+      <c r="I61" t="n">
+        <v>50</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>2</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Kang Fa 86</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Kang Fa 86</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3246,22 +3616,26 @@
       <c r="E62" t="n">
         <v>17</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
         <v>44917</v>
       </c>
-      <c r="G62" t="n">
-        <v>11</v>
-      </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" t="n">
+        <v>50</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>条帚门</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -3269,6 +3643,8 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3286,39 +3662,45 @@
         <v>45099</v>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
-      </c>
-      <c r="F63" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F63" t="n">
+        <v>40</v>
+      </c>
+      <c r="G63" s="2" t="n">
         <v>45100</v>
       </c>
-      <c r="G63" t="n">
-        <v>13</v>
-      </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" t="n">
+        <v>12</v>
+      </c>
+      <c r="I63" t="n">
+        <v>42</v>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>虾峙门</t>
         </is>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>2</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Hong Zhou You 27</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Kang Fa 86</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3336,24 +3718,28 @@
         <v>45099</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
-      </c>
-      <c r="F64" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F64" t="n">
+        <v>40</v>
+      </c>
+      <c r="G64" s="2" t="n">
         <v>45100</v>
       </c>
-      <c r="G64" t="n">
-        <v>13</v>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" t="n">
+        <v>12</v>
+      </c>
+      <c r="I64" t="n">
+        <v>42</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>虾峙门</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -3361,6 +3747,8 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3380,37 +3768,43 @@
       <c r="E65" t="n">
         <v>13</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2" t="n">
         <v>45123</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>14</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>虾峙门</t>
-        </is>
       </c>
       <c r="I65" t="n">
         <v>2</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>虾峙门</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>2</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t>Dong Gang You66</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Run Ze 11</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3430,22 +3824,26 @@
       <c r="E66" t="n">
         <v>13</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="n">
         <v>45123</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>14</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>虾峙门</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -3453,6 +3851,8 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/logs/duplicate_transactions_shell.xlsx
+++ b/logs/duplicate_transactions_shell.xlsx
@@ -559,7 +559,7 @@
         <v>45232</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
         <v>41</v>
@@ -615,7 +615,7 @@
         <v>45232</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>41</v>
@@ -654,7 +654,7 @@
         <v>45239</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>40</v>
@@ -706,7 +706,7 @@
         <v>45239</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
@@ -754,7 +754,7 @@
         <v>45439</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
         <v>41</v>
@@ -763,7 +763,7 @@
         <v>45440</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
         <v>47</v>
@@ -810,7 +810,7 @@
         <v>45439</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>41</v>
@@ -819,7 +819,7 @@
         <v>45440</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>47</v>
@@ -858,7 +858,7 @@
         <v>45303</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
         <v>42</v>
@@ -867,7 +867,7 @@
         <v>45304</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
         <v>42</v>
@@ -910,7 +910,7 @@
         <v>45303</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
         <v>42</v>
@@ -919,7 +919,7 @@
         <v>45304</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
         <v>42</v>
@@ -1064,10 +1064,10 @@
         <v>16</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="H12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>32</v>
@@ -1116,10 +1116,10 @@
         <v>16</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="H13" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>32</v>
@@ -1167,7 +1167,7 @@
         <v>45269</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" t="n">
         <v>33</v>
@@ -1219,7 +1219,7 @@
         <v>45269</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" t="n">
         <v>33</v>
@@ -1258,7 +1258,7 @@
         <v>45324</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
         <v>45</v>
@@ -1267,7 +1267,7 @@
         <v>45325</v>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" t="n">
         <v>45</v>
@@ -1314,7 +1314,7 @@
         <v>45324</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>45</v>
@@ -1323,7 +1323,7 @@
         <v>45325</v>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
         <v>45</v>
@@ -1362,7 +1362,7 @@
         <v>44934</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" t="n">
         <v>40</v>
@@ -1414,7 +1414,7 @@
         <v>44934</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
         <v>40</v>
@@ -1462,7 +1462,7 @@
         <v>44934</v>
       </c>
       <c r="E20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
         <v>40</v>
@@ -1519,7 +1519,7 @@
         <v>45102</v>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" t="n">
         <v>41</v>
@@ -1579,7 +1579,7 @@
         <v>45102</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
         <v>41</v>
@@ -1727,7 +1727,7 @@
         <v>45422</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
         <v>47</v>
@@ -1779,7 +1779,7 @@
         <v>45422</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I26" t="n">
         <v>47</v>
@@ -1818,7 +1818,7 @@
         <v>44990</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
         <v>55</v>
@@ -1874,7 +1874,7 @@
         <v>44990</v>
       </c>
       <c r="E28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
         <v>55</v>
@@ -1931,7 +1931,7 @@
         <v>45389</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
         <v>31</v>
@@ -1983,7 +1983,7 @@
         <v>45389</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>31</v>
@@ -2022,7 +2022,7 @@
         <v>45264</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
         <v>41</v>
@@ -2031,7 +2031,7 @@
         <v>45264</v>
       </c>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I31" t="n">
         <v>40</v>
@@ -2074,7 +2074,7 @@
         <v>45264</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
         <v>41</v>
@@ -2083,7 +2083,7 @@
         <v>45264</v>
       </c>
       <c r="H32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I32" t="n">
         <v>40</v>
@@ -2447,7 +2447,7 @@
         <v>45132</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
         <v>41</v>
@@ -2499,7 +2499,7 @@
         <v>45132</v>
       </c>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I40" t="n">
         <v>41</v>
@@ -2538,7 +2538,7 @@
         <v>45427</v>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
         <v>30</v>
@@ -2547,7 +2547,7 @@
         <v>45428</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
         <v>47</v>
@@ -2590,7 +2590,7 @@
         <v>45427</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F42" t="n">
         <v>30</v>
@@ -2599,7 +2599,7 @@
         <v>45428</v>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I42" t="n">
         <v>47</v>
@@ -2747,7 +2747,7 @@
         <v>45060</v>
       </c>
       <c r="H45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I45" t="n">
         <v>42</v>
@@ -2799,7 +2799,7 @@
         <v>45060</v>
       </c>
       <c r="H46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I46" t="n">
         <v>42</v>
@@ -2838,7 +2838,7 @@
         <v>45254</v>
       </c>
       <c r="E47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F47" t="n">
         <v>57</v>
@@ -2890,7 +2890,7 @@
         <v>45254</v>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F48" t="n">
         <v>57</v>
@@ -2947,7 +2947,7 @@
         <v>45245</v>
       </c>
       <c r="H49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I49" t="n">
         <v>40</v>
@@ -3003,7 +3003,7 @@
         <v>45245</v>
       </c>
       <c r="H50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I50" t="n">
         <v>40</v>
@@ -3051,7 +3051,7 @@
         <v>44999</v>
       </c>
       <c r="H51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I51" t="n">
         <v>40</v>
@@ -3107,7 +3107,7 @@
         <v>44999</v>
       </c>
       <c r="H52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I52" t="n">
         <v>40</v>
@@ -3155,7 +3155,7 @@
         <v>45187</v>
       </c>
       <c r="H53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I53" t="n">
         <v>59</v>
@@ -3207,7 +3207,7 @@
         <v>45187</v>
       </c>
       <c r="H54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I54" t="n">
         <v>59</v>
@@ -3255,7 +3255,7 @@
         <v>44954</v>
       </c>
       <c r="H55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I55" t="n">
         <v>56</v>
@@ -3315,7 +3315,7 @@
         <v>44954</v>
       </c>
       <c r="H56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I56" t="n">
         <v>56</v>
@@ -3354,7 +3354,7 @@
         <v>45248</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>55</v>
@@ -3363,7 +3363,7 @@
         <v>45249</v>
       </c>
       <c r="H57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I57" t="n">
         <v>42</v>
@@ -3406,7 +3406,7 @@
         <v>45248</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" t="n">
         <v>55</v>
@@ -3415,7 +3415,7 @@
         <v>45249</v>
       </c>
       <c r="H58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I58" t="n">
         <v>42</v>
@@ -3454,7 +3454,7 @@
         <v>45345</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
         <v>43</v>
@@ -3510,7 +3510,7 @@
         <v>45345</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
         <v>43</v>
@@ -3567,7 +3567,7 @@
         <v>44917</v>
       </c>
       <c r="H61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I61" t="n">
         <v>50</v>
@@ -3623,7 +3623,7 @@
         <v>44917</v>
       </c>
       <c r="H62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I62" t="n">
         <v>50</v>
@@ -3662,7 +3662,7 @@
         <v>45099</v>
       </c>
       <c r="E63" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F63" t="n">
         <v>40</v>
@@ -3671,7 +3671,7 @@
         <v>45100</v>
       </c>
       <c r="H63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I63" t="n">
         <v>42</v>
@@ -3718,7 +3718,7 @@
         <v>45099</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>40</v>
@@ -3727,7 +3727,7 @@
         <v>45100</v>
       </c>
       <c r="H64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I64" t="n">
         <v>42</v>
